--- a/04_Output/rC_DG.xlsx
+++ b/04_Output/rC_DG.xlsx
@@ -2933,11 +2933,11 @@
         <v>24480940.185</v>
       </c>
       <c r="G10" t="n">
-        <v>0.303866762065075</v>
+        <v>0.294833100435432</v>
       </c>
       <c r="H10"/>
       <c r="I10" t="n">
-        <v>-0.517316801865353</v>
+        <v>-0.530423760536601</v>
       </c>
     </row>
   </sheetData>
